--- a/光伏配储项目/电价数据/2026/畲江站.xlsx
+++ b/光伏配储项目/电价数据/2026/畲江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.41167</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.80122</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43427</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.02435</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.15986</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.02045</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.03829999999999999</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.10138</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.10534</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.09074</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.02697</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.53088</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.56526</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74498</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.15091</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.42478</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43476</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6696799999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.89838</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.50863</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.22107</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.35712</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.16487</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.06167</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31919</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.42245</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.71345</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7657200000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.15409</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95651</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9159299999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80987</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7726900000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5214099999999999</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49247</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47268</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43254</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73712</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.91414</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.98223</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51647</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5439400000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5240900000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.52424</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48551</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39217</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.48961</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.41849</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.48599</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.4326</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.34579</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.32584</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.5310499999999999</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.53871</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4926</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.27444</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.00256</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.20488</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.02164</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.15733</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.3981</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5491699999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.21596</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.01178</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.06858</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.03844</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.04171</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.44986</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6106200000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.78161</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.8201000000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.20049</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.46672</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15052</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.87366</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.23927</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.13444</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.32119</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.0736</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11879</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67618</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.01228</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.93306</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.99175</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.83702</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.19309</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9863999999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45651</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.95853</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.00517</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45588</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38056</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33563</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52523</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50358</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5043800000000001</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42287</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44072</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45822</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37397</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48983</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45256</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45049</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.02125</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.04886</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.06838</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.03997</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.80871</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.14716</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.02925</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.47457</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.55613</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5952799999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.34003</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6320399999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6741900000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47113</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50796</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.72697</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.88115</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.88309</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.98354</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.5007</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.75973</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.51601</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.63428</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.9084</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.59749</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9944</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8037799999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.67589</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.65208</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.78706</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4392200000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46277</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34313</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5124099999999999</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39464</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46094</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.42031</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.00017</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.004940000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.00019</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.01236</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.60725</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.41338</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.22923</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.20375</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6464099999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31436</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.52418</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.45925</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.61027</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.48226</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.5315700000000001</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47661</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40477</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.49602</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.56909</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.6547500000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.48533</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6085900000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.53032</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.50201</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50425</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.42094</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42922</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33389</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.01939</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.09175</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1341</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.01038</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03011</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.02962</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.09529</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.0978</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.02898</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.4409</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.37309</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.45497</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.45687</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.5002799999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.42769</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.44075</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.57845</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.38616</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.00121</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.5042</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.66024</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.6069199999999999</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.63144</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.39796</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.43305</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38863</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.47999</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.50932</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.46705</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.79062</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.45756</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.47693</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.4329</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10154</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04282</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.005650000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19787</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26311</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01144</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05202</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05019</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.36434</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.38851</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.35592</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33436</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.45108</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46042</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78572</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86971</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61209</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5555099999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.44308</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.36472</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.49415</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45809</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.43806</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.48165</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.72627</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.5518200000000001</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.6529700000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.87362</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.89105</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47622</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.55223</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.72781</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.53501</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.17264</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.9253899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8915599999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.5678799999999999</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>1.04835</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.96068</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6005</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34514</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.45683</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.52765</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.60221</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.53218</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.4816</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.46366</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.38472</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.94674</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5740700000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.51834</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.49042</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61252</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.5113799999999999</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.39236</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.69486</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.48267</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.44732</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.42776</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.10674</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2615</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27407</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26254</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2039</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29141</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3757200000000001</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26361</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38129</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.41959</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.46739</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.60075</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43556</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.49673</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.52038</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.5093299999999999</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.51305</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.91777</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.49489</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.14665</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.53377</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.25421</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.76225</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8559600000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.7121900000000001</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.9638300000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.70369</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.55314</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.48817</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.5452100000000001</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.52112</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.6965399999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.47851</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.53559</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.47694</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.57463</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.6200599999999999</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.43689</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4623</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.58384</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.51683</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.57517</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.43945</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.52564</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.53639</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.54131</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.47815</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.33657</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.68914</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.73434</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25519</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16416</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.00634</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26512</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.48307</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.38102</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.45229</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.4179</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.38709</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.7129800000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.6127100000000001</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.14635</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.62093</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5834600000000001</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.55489</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.46534</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.37772</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.40518</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.5884400000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.43289</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.44904</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.5319400000000001</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.36603</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.47566</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.48243</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.46939</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.50687</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.5067200000000001</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.50606</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.69897</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.47421</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.60336</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.71282</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.6238400000000001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.58285</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.44225</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.48463</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.52459</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.15854</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.48501</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.0456</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.00731</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28661</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.0342</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01463</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.00357</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.20241</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.01135</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25783</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.02187</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.03629</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.07557</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.03698</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.25712</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.41337</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.43171</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.47429</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.4591</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.49523</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.47905</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.61175</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.48709</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.51371</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.60653</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.5925</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.58611</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.5936900000000001</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.47454</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.43807</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.43082</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.43593</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.41906</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.39074</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.7757500000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.63409</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.5438200000000001</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.52966</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.44503</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.46488</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.4607</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.45534</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.41784</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.47901</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.43976</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.41355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.6064400000000001</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.46394</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.42331</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.38512</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.39342</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23774</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25923</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18689</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18187</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.1501</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21703</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24462</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.02737</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.27042</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.5626100000000001</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.39692</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.43835</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.44897</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.61672</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.45281</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.42281</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.41472</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.5202100000000001</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.38257</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.42136</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.42234</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.47723</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.45512</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.46339</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.41788</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.72029</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.40165</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.7252000000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.45646</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.38508</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.47481</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.42347</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.16817</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.46595</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.71472</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.54772</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.5182100000000001</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.40321</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.47593</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5522400000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26848</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.23162</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.47262</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.63563</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5297500000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.42297</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.47389</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.47083</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.63864</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.5102099999999999</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42305</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5007900000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.48201</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.75098</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.26713</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>1.05251</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.84236</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5427000000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.43066</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.91522</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.49062</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.44536</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5773400000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.46392</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.46625</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.40893</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.47421</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.47868</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.47841</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.48181</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.48843</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.50608</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.54344</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.5204500000000001</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.49488</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.41486</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.40057</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.36435</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.48659</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.5699099999999999</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.49324</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.39263</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.46425</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.39382</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.46303</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.50846</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.48919</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.58039</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.48916</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.52849</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.55204</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.47245</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.38179</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.39002</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.76281</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.37165</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.46153</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.39759</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.40413</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.38639</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.36465</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.44082</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.44889</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.5346900000000001</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.44273</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.40787</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.68713</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.33299</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.57329</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.44903</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.6128400000000001</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.5081</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.39547</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.42266</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.39142</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40888</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.39221</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.41099</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.46421</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.45475</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.38879</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.42577</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.17772</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.01104</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20825</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15724</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21753</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20449</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.25216</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.26925</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.42857</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.48133</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.56004</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.66484</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.61751</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.51286</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.70377</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.66149</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.69236</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.86787</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.71224</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.4482</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.83158</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.54806</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.46005</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.4683</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.54226</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.6910299999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.5274099999999999</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.44015</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.42066</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.65752</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.82467</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.7089099999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.04642</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.52112</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.49002</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.50903</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.5185700000000001</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.46442</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.5334099999999999</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.47084</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.52988</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.47581</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.5189900000000001</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.50205</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.52022</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.51054</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.62866</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.60987</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.84085</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.70347</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5979</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.68989</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.59285</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.48648</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.46652</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.50305</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.51988</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58428</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46585</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.5230499999999999</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.48981</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.40255</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65701</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7153200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.14473</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.4042</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.2263</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.44745</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.48205</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.5553899999999999</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.6669299999999999</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.59446</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.71701</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.72077</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.8025099999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.10905</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.39427</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.51712</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.08498</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.29398</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.07843</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.8198300000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.3479</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7993400000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.65338</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.7036100000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.6551900000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.6758</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.6567999999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.63205</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.51754</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.78846</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.54043</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.56913</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.60093</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46568</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.58272</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.44735</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.48993</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.65438</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.5143</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.52449</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.48581</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.46828</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.44543</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.44497</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.77583</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.4718</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.5027699999999999</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.5032300000000001</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.41076</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.44516</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3864</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4308</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.47204</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.41797</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02652</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7292999999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.47542</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55537</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.50302</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.24816</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.03219</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03753</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.26057</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.61421</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.55629</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.58177</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.44316</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45708</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.47753</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.42222</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.54092</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.5363</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4709100000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.44872</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.55003</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.43929</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.56465</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.5792999999999999</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.59397</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.5569299999999999</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.44033</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.52876</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.5277500000000001</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.51919</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.59497</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.74676</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.5679500000000001</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.6153500000000001</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.59302</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.53367</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.48084</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.70553</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.5740599999999999</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.56702</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.5484</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.54408</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.78218</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.45803</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.73698</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.54355</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.7570800000000001</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.50045</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.54311</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.70596</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.51579</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.5288099999999999</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.49255</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.52174</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.52916</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.53659</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.68708</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.54401</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.68486</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.71146</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.57375</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.46145</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.71458</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.00555</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.26234</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.08176</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.12603</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.13585</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29903</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.15862</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.08848</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25623</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.03854</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.01632</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.08216</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16693</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.23716</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.22545</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.23508</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41613</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.48408</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.42711</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.49161</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.5027699999999999</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.43842</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.50647</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.44702</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.49948</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.45884</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.53871</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.56629</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.53923</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.48097</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.49566</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.48254</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.48096</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.57251</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.5893200000000001</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.44551</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.54291</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.54437</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.4789</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.41799</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.43471</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.40732</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.63985</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.46832</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.6450499999999999</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.41084</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.5990700000000001</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.66189</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.64723</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.64723</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.63948</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.63948</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.64412</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.41855</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.6524</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.63948</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.64024</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.4507</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.66227</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.66171</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.6619299999999999</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.50541</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15575</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01434</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03792</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01178</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0353</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20781</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27018</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.6530499999999999</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.42212</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.42616</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.41141</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.44844</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.59726</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.41104</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.45844</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.4098</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.44464</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.40111</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.18949</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.5418200000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1.09672</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5885199999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.60064</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.6719700000000001</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.59204</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.5488</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.56304</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.55657</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.80657</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.5418999999999999</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.51195</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.83331</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.7330800000000001</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.83375</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.75758</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.82877</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.79759</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.75895</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.7895700000000001</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.8416399999999999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.75502</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.59356</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.68706</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.92326</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87222</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16146</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04353</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25441</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.47886</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.43308</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.48039</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.17362</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.35369</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.28659</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.01119</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.33182</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.15516</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.32634</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8736</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.87186</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.87597</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.97241</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.33861</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.32227</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.32841</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.41286</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.45173</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.45158</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.67428</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.03471</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.97211</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.53087</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.70511</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.5781900000000001</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.58375</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.41867</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.54384</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.6180800000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.44998</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.46933</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.45166</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.48396</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.77489</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.50969</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.5506799999999999</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.49866</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.53584</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.5418500000000001</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.78871</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.63415</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.59093</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.57594</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.69437</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.77288</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5625599999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.59412</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.43691</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.5259299999999999</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.05746</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.54192</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.11029</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.09562999999999999</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.24848</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25988</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.38964</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.4014</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.42565</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.44956</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.44198</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.71248</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.49659</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.5574</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.0704</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.68762</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.48313</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.6091299999999999</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.59909</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.53562</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.7722899999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.43481</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.45934</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.43056</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.44643</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.43428</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.53424</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.5578500000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.5210900000000001</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.48898</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.48215</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.47407</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.42191</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.38244</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.43445</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.40588</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.42167</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.6159199999999999</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.47067</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.44793</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00134</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.12636</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.98073</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.43667</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.90462</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.6882</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.43296</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.39539</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43007</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.47035</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.4162</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.85414</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.62352</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.51897</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.58061</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.8694299999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82921</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.66323</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.03307</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.92814</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.68477</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.6900700000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.46319</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.5346599999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.64323</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.45255</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.48238</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.48087</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.43842</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.41948</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.4269</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.56609</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.47187</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.48641</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.47095</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.44462</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.40633</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.44211</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.43446</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.41068</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.4117</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.4144</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.4362200000000001</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.5031</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.39101</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.41028</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.40578</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37928</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.40523</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.41908</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.39609</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.41014</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.42872</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.45751</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.47333</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45121</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.6639299999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.8159</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.63136</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.90154</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.93623</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.5917899999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.59241</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.8563999999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.54062</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.8770800000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.05815</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.80624</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.73403</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.74648</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.12402</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.5455099999999999</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.5387799999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.4680299999999999</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.42971</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.39071</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.43001</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.49793</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.78474</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.40462</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.45967</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.41767</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.5417999999999999</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.79326</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.55865</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.55502</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.46283</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.23979</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.19185</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24625</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03225</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.16696</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.02885</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01843</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.16895</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.18979</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03353</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05314</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27338</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23216</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24952</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.50337</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.52278</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.59956</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.8074</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.6599400000000001</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.55311</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.5216900000000001</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.48475</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.65062</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.5627300000000001</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.97368</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.58466</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.7844800000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.8391799999999999</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.6438700000000001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.65555</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.6179600000000001</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.52851</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.6755099999999999</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.64838</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.48113</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.80387</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57629</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5587300000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.66491</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.61548</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.6575700000000001</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.69135</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.71646</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.87709</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.72533</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.57039</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.6865</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.58345</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.6937000000000001</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.60201</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.5787599999999999</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.5456799999999999</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.55883</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.55374</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.62302</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.56565</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.56576</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.55974</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.55616</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.56336</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.55365</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.55398</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.53604</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.5493899999999999</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.56314</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.5453300000000001</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.53859</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.5762200000000001</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.51004</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.5343</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.54408</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.54944</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.53525</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.50178</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.5142899999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.45734</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26553</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.14624</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23548</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.11065</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.2757</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42523</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35279</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.40389</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.44632</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.48924</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.48084</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.45772</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.5222899999999999</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.51754</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.49891</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.56553</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.5199199999999999</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.64371</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.75551</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.5455099999999999</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.5234500000000001</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.57426</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.6660499999999999</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.59665</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.55343</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.5302</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42258</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.58436</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.60434</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.49543</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.52362</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.51458</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.5123099999999999</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.52139</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.7347400000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.52798</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.83747</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.52039</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.52544</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.57097</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.58524</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.57021</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.57182</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.55223</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.5298200000000001</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.48999</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.6403099999999999</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.44563</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.40666</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.5319700000000001</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.58854</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.5722699999999999</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.55413</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.5487300000000001</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.5176799999999999</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.53059</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.5354099999999999</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.54447</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.44285</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.54052</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.50573</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.51897</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14644</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19965</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23708</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04719</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04746</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13386</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.00018</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17713</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22785</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15783</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24223</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.21993</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.00203</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20203</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.15138</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36468</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47334</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.42948</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.46217</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.5861900000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.7123700000000001</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6577000000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.56779</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.56824</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5471699999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.54172</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.58217</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.49739</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.53071</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6767000000000001</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5953999999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5413600000000001</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.5125599999999999</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.5241399999999999</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.51042</v>
       </c>
     </row>
   </sheetData>
